--- a/data/trans_dic/IP1009-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos intestinales crónicos</t>
+          <t>Menores que padecen transtornos intestinales crónicos (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,59</t>
+          <t>0,22; 2,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,4</t>
+          <t>0,1; 1,17</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,94</t>
+          <t>0,11; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,81</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,92</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,52</t>
+          <t>0,08; 0,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,77</t>
+          <t>0,16; 0,74</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos intestinales crónicos (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4165</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4088</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3411</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>449; 4940</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4011</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3237</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4427</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3796</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4416</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3506</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2816</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3303</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3364</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2988</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3936</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>454; 5074</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3967</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3460</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3741</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3598</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4881</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2585</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3153</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3640</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4574</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>758; 6513</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5512</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3121</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>719; 6617</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1096; 6543</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>619; 5155</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2258; 10204</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1009-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Clase-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,99</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,45</t>
+          <t>0,22; 2,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,17</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,97</t>
+          <t>0,11; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,93</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,49</t>
+          <t>0,09; 0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,74</t>
+          <t>0,17; 0,7</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4165</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 3076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3411</t>
+          <t>0; 3862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>449; 4940</t>
+          <t>446; 5196</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 3741</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3237</t>
+          <t>0; 3151</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4427</t>
+          <t>0; 5378</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3796</t>
+          <t>0; 3231</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4416</t>
+          <t>0; 4889</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 3467</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2816</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3303</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 4364</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>0; 2777</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2988</t>
+          <t>0; 2968</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3936</t>
+          <t>0; 4779</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>454; 5074</t>
+          <t>454; 4680</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3967</t>
+          <t>0; 3481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3460</t>
+          <t>0; 3293</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3741</t>
+          <t>0; 2992</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3598</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4881</t>
+          <t>0; 4338</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3640</t>
+          <t>0; 3431</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4574</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>758; 6513</t>
+          <t>767; 6691</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 5527</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3121</t>
+          <t>0; 3515</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>719; 6617</t>
+          <t>711; 6416</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1096; 6543</t>
+          <t>1144; 6915</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>619; 5155</t>
+          <t>619; 5124</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2258; 10204</t>
+          <t>2402; 9706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1009-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1009-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,57</t>
+          <t>0,22; 2,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -740,27 +740,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,1; 1,4</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>0,99%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,37</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,1; 0,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,0</t>
+          <t>0,1; 0,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,49</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,9</t>
+          <t>0,11; 0,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,52</t>
+          <t>0,08; 0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,37</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,7</t>
+          <t>0,18; 0,77</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>753</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3403</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3862</t>
+          <t>0; 4017</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3789</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>446; 5196</t>
+          <t>450; 5239</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3741</t>
+          <t>0; 4212</t>
         </is>
       </c>
     </row>
@@ -1701,27 +1701,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3151</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3150</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5378</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3231</t>
+          <t>0; 2938</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>0; 4941</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4178</t>
+          <t>0; 3453</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2032,22 +2032,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2080,27 +2080,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1227</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>0; 3083</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4364</t>
+          <t>0; 3494</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2777</t>
+          <t>0; 3716</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2968</t>
+          <t>0; 3907</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4779</t>
+          <t>0; 4361</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>454; 4680</t>
+          <t>455; 6085</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3899</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3481</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 2807</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2411,22 +2411,22 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>605</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2992</t>
+          <t>0; 3964</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4338</t>
+          <t>0; 4636</t>
         </is>
       </c>
     </row>
@@ -2511,27 +2511,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2585</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3431</t>
+          <t>676; 5531</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5216</t>
+          <t>0; 2930</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>767; 6691</t>
+          <t>713; 6553</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5527</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3515</t>
+          <t>0; 5259</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>711; 6416</t>
+          <t>763; 6310</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1144; 6915</t>
+          <t>1081; 6826</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>619; 5124</t>
+          <t>618; 5756</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2402; 9706</t>
+          <t>2472; 10597</t>
         </is>
       </c>
     </row>
